--- a/Class 2 uncertainty md.xlsx
+++ b/Class 2 uncertainty md.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521FB147-9F1C-4E1F-A46E-403917062112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C23EFE7-B83C-40E8-9640-56ECE59CDD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31965" yWindow="2820" windowWidth="21600" windowHeight="11235" xr2:uid="{18E10DD8-E55E-4606-9FC3-D56037DC8C39}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18E10DD8-E55E-4606-9FC3-D56037DC8C39}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
